--- a/sample-data/split/Trip Master.xlsx
+++ b/sample-data/split/Trip Master.xlsx
@@ -56,13 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,104 +452,104 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Students</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Paste the share link of the Students spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Trips</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Paste the share link of the Trips spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Itinerary</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Paste the share link of the Itinerary spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Paste the share link of the Documents spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Guidelines</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Paste the share link of the Guidelines spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Reminders</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Paste the share link of the Reminders spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Travel</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Paste the share link of the Travel spreadsheet here.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Paste the share link of the Media spreadsheet here.</t>
         </is>
